--- a/training_time.xlsx
+++ b/training_time.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\ACOPF-feasible\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E47645E-CCD6-4FA1-A1EE-CF84571D14F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6B9892-5A7F-4218-9641-133BCAB4E258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -102,6 +113,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{0CCE15A6-1D86-445D-857F-746395F5067B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8266_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{3C6CE0CC-1CEC-4D7A-BC85-30F93EE970E5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8267_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B3" authorId="0" shapeId="0" xr:uid="{BFD44F9C-BF3B-4A15-90BF-846CEE4AA9AB}">
       <text>
         <r>
@@ -174,6 +233,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{74019C07-A6FD-46AC-9224-F696A749B1E2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8268_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{ED3F8E03-8BE2-473A-A8AF-14CA5C753E9A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8269_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{23B3DCC1-5036-4E8C-801B-7B34E5A24CFD}">
       <text>
         <r>
@@ -246,6 +353,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{20F52A64-D86F-45CD-BE5A-09D95E411DDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8270_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{8A8B99C9-4FBC-416D-980B-65F7F9236BC1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8271_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0" xr:uid="{E4C696F6-99AC-44B4-B0F0-C075DD32ED1C}">
       <text>
         <r>
@@ -366,6 +521,246 @@
         </r>
       </text>
     </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{39002DCC-0B4C-43C3-8888-05CDA3EAF65B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8262_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{1C6D57E8-CD1B-4716-8C8F-9BDBD92DB445}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8263_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{CEAF22BB-FB13-4B05-B984-E18B3EFA1A73}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8264_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{73B99BF4-E137-41FD-8F57-5CFC398F63AA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8301_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{92DF15CB-491D-4DD9-B0C6-745E6A481689}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8302_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{F1AB6BE6-4662-4362-A60D-E3AD53121D24}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8276_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{49484F10-8E38-4B99-AF4D-46086B4E5273}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8277_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{F76658EE-790C-433C-AADB-625D0D5A5F56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8278_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{097B421D-62E2-434F-984B-6FA9C2BEA728}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8279_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{4BB6ADD9-E569-461B-8710-8C5C3D6F14E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8280_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B10" authorId="0" shapeId="0" xr:uid="{FE44CD18-E7B7-4934-BD81-9874D6F0A55A}">
       <text>
         <r>
@@ -438,6 +833,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{326C6A85-3642-41F2-9A61-978C6F660298}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8272_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{5038C468-4CC3-4C20-B6E1-02C23310283B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8273_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B11" authorId="0" shapeId="0" xr:uid="{AFAEA203-7CB8-48AB-AB11-16F2FD08D7F9}">
       <text>
         <r>
@@ -510,6 +953,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{3FF77FBB-8FF2-4C43-938E-3147A454A159}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8274_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{C25590AB-14CB-4227-B45C-8C272D984C7A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+8275_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B12" authorId="0" shapeId="0" xr:uid="{45268F24-C864-4397-A9BC-6004C8F55F9E}">
       <text>
         <r>
@@ -603,6 +1094,150 @@
           </rPr>
           <t xml:space="preserve">
 8242_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{462FD50D-2BBB-4D65-A408-51015307A832}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8303_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{2834658D-0BE0-4056-8A95-B29FD67547E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8308_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{BC3F3FBB-0DDA-4181-A231-6F3AA4CE91F8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8309_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{5A2DCA70-C7F7-4C42-8727-210D2CB51F12}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8310_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{B05586A1-0A50-4331-9862-C51005930F05}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8311_acopf_ISS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{EA92CB7B-137E-4838-98C9-644CEBBEB6BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Muhammad Firdaus:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8312_acopf_ISS</t>
         </r>
       </text>
     </comment>
@@ -611,7 +1246,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>Ours</t>
   </si>
@@ -640,14 +1275,20 @@
     <t xml:space="preserve">last </t>
   </si>
   <si>
-    <t>8251_acopf_ISS</t>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>8312_acopf_ISS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,6 +1308,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -971,18 +1625,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -995,8 +1655,22 @@
       <c r="D2">
         <v>9.66</v>
       </c>
+      <c r="E2">
+        <v>9.5</v>
+      </c>
+      <c r="F2">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="H2">
+        <f>AVERAGE(B2:F2)</f>
+        <v>9.6100000000000012</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.STDEV.S(B2:F2)</f>
+        <v>8.9442719099992019E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1009,8 +1683,22 @@
       <c r="D3">
         <v>17.8</v>
       </c>
+      <c r="E3">
+        <v>17.71</v>
+      </c>
+      <c r="F3">
+        <v>17.8</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H6" si="0">AVERAGE(B3:F3)</f>
+        <v>17.826000000000001</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I6" si="1">_xlfn.STDEV.S(B3:F3)</f>
+        <v>9.5026312145636102E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1024,10 +1712,21 @@
         <v>33.950000000000003</v>
       </c>
       <c r="E4">
-        <v>33.090000000000003</v>
+        <v>33.17</v>
+      </c>
+      <c r="F4">
+        <v>33.479999999999997</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>33.36</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>0.36537651812890232</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1046,13 +1745,44 @@
       <c r="F5">
         <v>10.02</v>
       </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>9.8719999999999999</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>0.16115210206509828</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>38.69</v>
+      </c>
+      <c r="C6">
+        <v>38.409999999999997</v>
+      </c>
+      <c r="D6">
+        <v>38</v>
+      </c>
+      <c r="E6">
+        <v>37.86</v>
+      </c>
+      <c r="F6">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>38.231999999999992</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>0.32965133095438764</v>
+      </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1060,12 +1790,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
+      <c r="B9">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="C9">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="D9">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="E9">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="F9">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:H13" si="2">AVERAGE(B9:F9)</f>
+        <v>10.044</v>
+      </c>
+      <c r="I9">
+        <f t="shared" ref="I9:I13" si="3">_xlfn.STDEV.S(B9:F9)</f>
+        <v>8.9442719099998621E-3</v>
+      </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1078,8 +1831,22 @@
       <c r="D10">
         <v>18.170000000000002</v>
       </c>
+      <c r="E10">
+        <v>18.34</v>
+      </c>
+      <c r="F10">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>18.244000000000003</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>6.3482280992414972E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1092,8 +1859,22 @@
       <c r="D11">
         <v>33.46</v>
       </c>
+      <c r="E11">
+        <v>33.42</v>
+      </c>
+      <c r="F11">
+        <v>33.68</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>33.510000000000005</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>0.1048808848170141</v>
+      </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1109,10 +1890,44 @@
       <c r="E12">
         <v>10.130000000000001</v>
       </c>
+      <c r="F12">
+        <v>10.24</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>10.238000000000001</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>6.3796551630945719E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
+      </c>
+      <c r="B13">
+        <v>38.630000000000003</v>
+      </c>
+      <c r="C13">
+        <v>38.6</v>
+      </c>
+      <c r="D13">
+        <v>38.5</v>
+      </c>
+      <c r="E13">
+        <v>38.6</v>
+      </c>
+      <c r="F13">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>38.67</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>0.20174241001832113</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1120,7 +1935,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
